--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -18,13 +18,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="basefont"/>
+      <sz val="9.0"/>
+      <color rgb="002D3C51"/>
+      <u val="none"/>
     </font>
     <font>
       <name val="basefont"/>
@@ -264,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
@@ -282,6 +288,9 @@
       <alignment wrapText="true" horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFill="true" applyBorder="true" applyFont="true">
+      <alignment wrapText="true" horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -400,7 +409,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>바이오진단임상병리전공</t>
         </is>
@@ -440,7 +449,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M2" s="6"/>
+      <c r="M2" s="7"/>
     </row>
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
@@ -463,7 +472,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>바이오진단임상병리전공</t>
         </is>
@@ -503,7 +512,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M3" s="6"/>
+      <c r="M3" s="7"/>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
@@ -526,7 +535,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>바이오진단임상병리전공</t>
         </is>
@@ -566,7 +575,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M4" s="6"/>
+      <c r="M4" s="7"/>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -589,7 +598,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>바이오진단임상병리전공</t>
         </is>
@@ -629,7 +638,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M5" s="6"/>
+      <c r="M5" s="7"/>
     </row>
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
@@ -652,7 +661,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>바이오진단임상병리전공</t>
         </is>
@@ -692,7 +701,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M6" s="6"/>
+      <c r="M6" s="7"/>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
@@ -715,7 +724,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>바이오진단임상병리전공</t>
         </is>
@@ -755,7 +764,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M7" s="6"/>
+      <c r="M7" s="7"/>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
@@ -778,7 +787,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>바이오진단임상병리전공</t>
         </is>
@@ -818,7 +827,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M8" s="6"/>
+      <c r="M8" s="7"/>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
@@ -841,7 +850,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>의료융합방사선기술전공</t>
         </is>
@@ -881,7 +890,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M9" s="6"/>
+      <c r="M9" s="7"/>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
@@ -904,7 +913,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>의료융합방사선기술전공</t>
         </is>
@@ -944,7 +953,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M10" s="6"/>
+      <c r="M10" s="7"/>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
@@ -967,7 +976,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>의료융합방사선기술전공</t>
         </is>
@@ -1007,7 +1016,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M11" s="6"/>
+      <c r="M11" s="7"/>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
@@ -1030,7 +1039,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>의료융합방사선기술전공</t>
         </is>
@@ -1070,7 +1079,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M12" s="6"/>
+      <c r="M12" s="7"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
@@ -1093,7 +1102,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>의료융합방사선기술전공</t>
         </is>
@@ -1133,7 +1142,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M13" s="6"/>
+      <c r="M13" s="7"/>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
@@ -1156,7 +1165,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>의료융합방사선기술전공</t>
         </is>
@@ -1196,7 +1205,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M14" s="6"/>
+      <c r="M14" s="7"/>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
@@ -1219,7 +1228,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>의료융합방사선기술전공</t>
         </is>
@@ -1259,7 +1268,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M15" s="6"/>
+      <c r="M15" s="7"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
@@ -1282,7 +1291,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>의료융합방사선기술전공</t>
         </is>
@@ -1322,7 +1331,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M16" s="6"/>
+      <c r="M16" s="7"/>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
@@ -1345,7 +1354,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>의료융합방사선기술전공</t>
         </is>
@@ -1385,7 +1394,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1412,7 +1421,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>의료융합방사선기술전공</t>
         </is>
@@ -1452,7 +1461,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M18" s="6"/>
+      <c r="M18" s="7"/>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
@@ -1475,7 +1484,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>맞춤형전문도수치료전공</t>
         </is>
@@ -1515,7 +1524,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M19" s="6"/>
+      <c r="M19" s="7"/>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
@@ -1538,7 +1547,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>맞춤형전문도수치료전공</t>
         </is>
@@ -1578,7 +1587,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M20" s="6"/>
+      <c r="M20" s="7"/>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
@@ -1601,7 +1610,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>맞춤형전문도수치료전공</t>
         </is>
@@ -1641,7 +1650,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M21" s="6"/>
+      <c r="M21" s="7"/>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
@@ -1664,7 +1673,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>맞춤형전문도수치료전공</t>
         </is>
@@ -1704,7 +1713,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M22" s="6"/>
+      <c r="M22" s="7"/>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
@@ -1727,7 +1736,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>맞춤형전문도수치료전공</t>
         </is>
@@ -1767,7 +1776,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M23" s="6"/>
+      <c r="M23" s="7"/>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
@@ -1790,7 +1799,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>신기술덴탈헬스케어전공</t>
         </is>
@@ -1830,7 +1839,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M24" s="6"/>
+      <c r="M24" s="7"/>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
@@ -1853,7 +1862,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>신기술덴탈헬스케어전공</t>
         </is>
@@ -1893,7 +1902,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M25" s="6"/>
+      <c r="M25" s="7"/>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
@@ -1916,7 +1925,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>신기술덴탈헬스케어전공</t>
         </is>
@@ -1956,7 +1965,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M26" s="6"/>
+      <c r="M26" s="7"/>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
@@ -1979,7 +1988,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>신기술덴탈헬스케어전공</t>
         </is>
@@ -2019,7 +2028,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M27" s="6"/>
+      <c r="M27" s="7"/>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
@@ -2042,7 +2051,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>스마트뷰티헬스케어전공</t>
         </is>
@@ -2082,7 +2091,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M28" s="6"/>
+      <c r="M28" s="7"/>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
@@ -2105,7 +2114,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>스마트뷰티헬스케어전공</t>
         </is>
@@ -2145,7 +2154,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M29" s="6"/>
+      <c r="M29" s="7"/>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
@@ -2168,7 +2177,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>스마트뷰티헬스케어전공</t>
         </is>
@@ -2208,7 +2217,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M30" s="6"/>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
@@ -2231,7 +2244,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>스마트뷰티헬스케어전공</t>
         </is>
@@ -2271,7 +2284,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M31" s="6"/>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
@@ -2294,7 +2311,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>스마트융합치위생전공</t>
         </is>
@@ -2334,7 +2351,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M32" s="6"/>
+      <c r="M32" s="7"/>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
@@ -2357,7 +2374,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>스마트융합치위생전공</t>
         </is>
@@ -2397,7 +2414,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M33" s="6"/>
+      <c r="M33" s="7"/>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
@@ -2420,7 +2437,7 @@
           <t>바이오헬스융합학과</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>임상기반전문작업치료전공</t>
         </is>
@@ -2460,7 +2477,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M34" s="6"/>
+      <c r="M34" s="7"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -1965,7 +1965,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M26" s="7"/>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
@@ -2154,7 +2158,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M29" s="7"/>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -449,7 +449,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M2" s="7"/>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -894,7 +894,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M9" s="7"/>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
@@ -1083,7 +1087,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M12" s="7"/>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
@@ -1465,7 +1473,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M18" s="7"/>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -516,7 +516,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M3" s="7"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -1544,7 +1544,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M19" s="7"/>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
@@ -1607,7 +1611,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M20" s="7"/>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
@@ -1733,7 +1741,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M22" s="7"/>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
@@ -1796,7 +1808,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M23" s="7"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -709,7 +709,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M6" s="7"/>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -1682,7 +1682,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M21" s="7"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -1883,7 +1883,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M24" s="7"/>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
@@ -1946,7 +1950,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M25" s="7"/>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
@@ -2076,7 +2084,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M27" s="7"/>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
@@ -2466,7 +2478,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M33" s="7"/>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -646,7 +646,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M5" s="7"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -843,7 +843,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M8" s="7"/>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
@@ -973,7 +977,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M10" s="7"/>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
@@ -1292,7 +1300,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M15" s="7"/>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
@@ -1355,7 +1367,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M16" s="7"/>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -18,19 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="basefont"/>
-      <sz val="9.0"/>
-      <color rgb="002D3C51"/>
-      <u val="none"/>
     </font>
     <font>
       <name val="basefont"/>
@@ -270,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="center" vertical="center"/>
@@ -289,9 +283,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFill="true" applyBorder="true" applyFont="true">
       <alignment wrapText="true" horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="22" xfId="0" applyFill="true" applyBorder="true" applyFont="true">
-      <alignment wrapText="true" horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -449,7 +440,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -516,7 +507,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -583,7 +574,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M4" s="7"/>
+      <c r="M4" s="4"/>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -646,7 +637,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -713,7 +704,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -780,7 +771,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M7" s="7"/>
+      <c r="M7" s="4"/>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
@@ -843,7 +834,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -910,7 +901,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M9" s="7" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -977,7 +968,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1044,7 +1035,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M11" s="7"/>
+      <c r="M11" s="4"/>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
@@ -1107,7 +1098,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1174,7 +1165,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M13" s="7"/>
+      <c r="M13" s="4"/>
     </row>
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
@@ -1237,7 +1228,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M14" s="7"/>
+      <c r="M14" s="4"/>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
@@ -1300,7 +1291,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1367,7 +1358,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1434,7 +1425,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1501,7 +1492,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1568,7 +1559,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1635,7 +1626,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M20" s="7" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1702,7 +1693,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1769,7 +1760,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M22" s="7" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1836,7 +1827,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M23" s="7" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1903,7 +1894,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M24" s="7" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -1970,7 +1961,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M25" s="7" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2037,7 +2028,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M26" s="7" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2104,7 +2095,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2171,7 +2162,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M28" s="7"/>
+      <c r="M28" s="4"/>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
@@ -2234,7 +2225,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M29" s="7" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2301,7 +2292,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M30" s="7" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2368,7 +2359,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M31" s="7" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2435,7 +2426,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M32" s="7"/>
+      <c r="M32" s="4"/>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
@@ -2498,7 +2489,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -2565,7 +2556,7 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M34" s="7"/>
+      <c r="M34" s="4"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -1035,7 +1035,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M11" s="4"/>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -2166,7 +2166,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M28" s="4"/>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">

--- a/data_대학원.xlsx
+++ b/data_대학원.xlsx
@@ -2434,7 +2434,11 @@
           <t>재직</t>
         </is>
       </c>
-      <c r="M32" s="4"/>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
